--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="504">
   <si>
     <t>Filename</t>
   </si>
@@ -808,736 +808,724 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9858,0.0038,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0039,0.0001,0.0001,0.9990</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0008,0.0001,0.0000</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9971,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9892,0.0007,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.0915,0.0013,0.8918,0.0014</t>
+  </si>
+  <si>
+    <t>0.0389,0.0040,0.9624,0.0003</t>
+  </si>
+  <si>
+    <t>0.0031,0.0002,0.9942,0.0019</t>
+  </si>
+  <si>
+    <t>0.9761,0.0022,0.0091,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9979,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0320,0.9481,0.0094,0.0011</t>
+  </si>
+  <si>
+    <t>0.0004,0.9989,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.6929,0.0002,0.3207,0.0017</t>
+  </si>
+  <si>
+    <t>0.5922,0.0003,0.4886,0.0006</t>
+  </si>
+  <si>
+    <t>0.2643,0.0004,0.7522,0.0015</t>
+  </si>
+  <si>
+    <t>0.0058,0.0007,0.9913,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9995,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.8893,0.0855,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.0437,0.0142,0.9264,0.0023</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9998,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.9988,0.0031,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0006,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.8938,0.0004,0.1414,0.0002</t>
+  </si>
+  <si>
+    <t>0.0797,0.9244,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.0004,0.9986,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.9389,0.0143,0.3461</t>
+  </si>
+  <si>
+    <t>0.0035,0.0019,0.9876,0.0046</t>
+  </si>
+  <si>
+    <t>0.0003,0.0012,0.9979,0.0010</t>
+  </si>
+  <si>
+    <t>0.0039,0.0001,0.9950,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.1120,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0061,0.9981,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.0003,0.9992</t>
+  </si>
+  <si>
+    <t>0.0003,0.9991,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9984,0.0313,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0525,0.9877,0.0013</t>
+  </si>
+  <si>
+    <t>0.0007,0.0835,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9982,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0017,0.9995,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0015,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9964,0.0006,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.9999,0.0582</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9947,0.0010,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.0001,0.9705,0.9761,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.9998,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.3302,0.9672,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0061</t>
+  </si>
+  <si>
+    <t>0.0005,0.9985,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9278,0.0006,0.0953,0.0001</t>
+  </si>
+  <si>
+    <t>0.8338,0.0050,0.1127,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0012,0.9994,0.0033</t>
+  </si>
+  <si>
+    <t>0.0000,0.9618,0.9919,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9877,0.9865,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9923,0.9886,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0262,0.9982</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.9969,0.1089,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.9923,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9685,0.7775,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9960,0.6477,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9950,0.8241,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9560,0.9923,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0009,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0040,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0021,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0008,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9993,0.0003,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9896,0.0011,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.0162,0.0002,0.9808,0.0029</t>
-  </si>
-  <si>
-    <t>0.2683,0.0074,0.6834,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9988,0.0005</t>
-  </si>
-  <si>
-    <t>0.9668,0.0015,0.0204,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9982,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.9922,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0003,0.0000</t>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0020,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9933,0.0062,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0217,0.0006,0.9750,0.0012</t>
+  </si>
+  <si>
+    <t>0.9975,0.0001,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9971,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.0052,0.9862,0.0042,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.2429,0.7149,0.0245,0.0004</t>
+  </si>
+  <si>
+    <t>0.6000,0.0021,0.2309,0.0366</t>
+  </si>
+  <si>
+    <t>0.5353,0.0008,0.4011,0.0052</t>
+  </si>
+  <si>
+    <t>0.1683,0.0798,0.3347,0.0052</t>
+  </si>
+  <si>
+    <t>0.0986,0.0550,0.6678,0.0034</t>
+  </si>
+  <si>
+    <t>0.0000,0.0507,0.0001,0.9992</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.2621,0.0005,0.7344,0.0025</t>
-  </si>
-  <si>
-    <t>0.4890,0.0011,0.5407,0.0014</t>
-  </si>
-  <si>
-    <t>0.0017,0.0009,0.9951,0.0008</t>
-  </si>
-  <si>
-    <t>0.0028,0.0014,0.9916,0.0014</t>
-  </si>
-  <si>
-    <t>0.0182,0.0001,0.9868,0.0002</t>
-  </si>
-  <si>
-    <t>0.0084,0.0002,0.9922,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1080,0.8881,0.0016,0.0021</t>
-  </si>
-  <si>
-    <t>0.3126,0.0144,0.6276,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0035,0.9902,0.0093,0.0004</t>
-  </si>
-  <si>
-    <t>0.9973,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9488,0.0010,0.0409,0.0005</t>
-  </si>
-  <si>
-    <t>0.7803,0.2387,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.0029,0.9951,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0085,0.5954,0.2847,0.1167</t>
-  </si>
-  <si>
-    <t>0.0074,0.0016,0.9572,0.0330</t>
-  </si>
-  <si>
-    <t>0.0009,0.0039,0.9966,0.0007</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9979,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.1745,0.9951,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.0050,0.9965,0.0012</t>
-  </si>
-  <si>
-    <t>0.0002,0.0022,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0004,0.9989,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9968,0.0339,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0429,0.9982,0.0003</t>
-  </si>
-  <si>
-    <t>0.0017,0.0426,0.9905,0.0002</t>
-  </si>
-  <si>
-    <t>0.0039,0.0002,0.9954,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.9962,0.0009,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9962,0.0007,0.0008,0.0016</t>
-  </si>
-  <si>
-    <t>0.9975,0.0008,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0033,0.9999,0.0076</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0043,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9805,0.0110,0.0018,0.0019</t>
-  </si>
-  <si>
-    <t>0.0000,0.5386,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0010,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0108,0.0051,0.9681,0.0060</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.8985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0055</t>
-  </si>
-  <si>
-    <t>0.0059,0.9906,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9287,0.0002,0.1046,0.0002</t>
-  </si>
-  <si>
-    <t>0.9929,0.0009,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0013,0.9996,0.0025</t>
-  </si>
-  <si>
-    <t>0.0000,0.9882,0.9861,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9672,0.9672,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.0051,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9708,0.9816,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0062,0.9988</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9976,0.0239,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9741,0.8126,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9831,0.5383,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9652,0.9929,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9930,0.9243,0.0000</t>
+    <t>0.0000,0.9949,0.9792,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9978,0.0020,0.0000</t>
+  </si>
+  <si>
+    <t>0.0890,0.9236,0.0034,0.0003</t>
+  </si>
+  <si>
+    <t>0.8608,0.1569,0.0044,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0010,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9597,0.9916,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.7459,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.0180,0.9849,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.0012,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2960,0.0013,0.6733,0.0078</t>
+  </si>
+  <si>
+    <t>0.1380,0.0001,0.9106,0.0004</t>
+  </si>
+  <si>
+    <t>0.9436,0.0038,0.0278,0.0007</t>
+  </si>
+  <si>
+    <t>0.1263,0.0000,0.0000,0.9808</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0184,0.9990</t>
+  </si>
+  <si>
+    <t>0.0000,0.9918,0.9920,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0453,0.9417,0.0009,0.0029</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.2038,0.7985,0.0041,0.0006</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9688,0.0001,0.0000,0.0395</t>
+  </si>
+  <si>
+    <t>0.0002,0.0772,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.9736,0.0001,0.0003,0.0380</t>
+  </si>
+  <si>
+    <t>0.9977,0.0000,0.0001,0.0035</t>
+  </si>
+  <si>
+    <t>0.7670,0.1689,0.0058,0.0009</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0358,0.8444,0.0325,0.0046</t>
+  </si>
+  <si>
+    <t>0.9772,0.0069,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0004,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0008,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9958,0.0008,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9674,0.0307,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9537,0.0165,0.0091,0.0014</t>
+  </si>
+  <si>
+    <t>0.0250,0.9626,0.0077,0.0005</t>
+  </si>
+  <si>
+    <t>0.1984,0.1962,0.6698,0.0015</t>
+  </si>
+  <si>
+    <t>0.9402,0.1240,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9977,0.0005,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9522,0.0320,0.0019,0.0036</t>
+  </si>
+  <si>
+    <t>0.0000,0.0281,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9873,0.0036,0.0037,0.0023</t>
+  </si>
+  <si>
+    <t>0.0011,0.0004,0.9979,0.0004</t>
+  </si>
+  <si>
+    <t>0.0043,0.0048,0.9875,0.0044</t>
+  </si>
+  <si>
+    <t>0.0046,0.0004,0.9959,0.0006</t>
+  </si>
+  <si>
+    <t>0.0011,0.0007,0.9977,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0029,0.9956,0.0013</t>
+  </si>
+  <si>
+    <t>0.0386,0.0014,0.9673,0.0005</t>
+  </si>
+  <si>
+    <t>0.0091,0.0041,0.9784,0.0010</t>
+  </si>
+  <si>
+    <t>0.1606,0.0912,0.4831,0.0003</t>
+  </si>
+  <si>
+    <t>0.0123,0.6968,0.2519,0.0019</t>
+  </si>
+  <si>
+    <t>0.0032,0.0009,0.9956,0.0001</t>
+  </si>
+  <si>
+    <t>0.2525,0.0137,0.4753,0.0087</t>
+  </si>
+  <si>
+    <t>0.2718,0.0016,0.7052,0.0036</t>
+  </si>
+  <si>
+    <t>0.0178,0.9690,0.0110,0.0007</t>
+  </si>
+  <si>
+    <t>0.0018,0.9951,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.1603,0.8725,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.8503,0.2161,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.1285,0.9232,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0003,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9817,0.0008,0.0124,0.0000</t>
+  </si>
+  <si>
+    <t>0.9253,0.0001,0.0146,0.0072</t>
+  </si>
+  <si>
+    <t>0.4582,0.0112,0.5315,0.0002</t>
+  </si>
+  <si>
+    <t>0.0292,0.0007,0.9725,0.0009</t>
+  </si>
+  <si>
+    <t>0.0011,0.0000,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0421,0.9935,0.0025</t>
+  </si>
+  <si>
+    <t>0.0116,0.0023,0.9815,0.0011</t>
+  </si>
+  <si>
+    <t>0.0192,0.0026,0.9631,0.0031</t>
+  </si>
+  <si>
+    <t>0.0024,0.2064,0.9422,0.0011</t>
+  </si>
+  <si>
+    <t>0.9973,0.0015,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9422,0.0800,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.9943,0.0031,0.0002,0.0005</t>
   </si>
   <si>
     <t>0.9995,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9988,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9918,0.0067,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9952,0.0059,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0026,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9854,0.0128,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9971,0.0019,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0015,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9996,0.0014</t>
-  </si>
-  <si>
-    <t>0.0052,0.0004,0.9935,0.0004</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0002,0.9980,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.9990,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.9918,0.0032,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.9949,0.0016,0.0004</t>
-  </si>
-  <si>
-    <t>0.7732,0.2581,0.0034,0.0003</t>
-  </si>
-  <si>
-    <t>0.4112,0.0018,0.5793,0.0037</t>
-  </si>
-  <si>
-    <t>0.1078,0.0005,0.8949,0.0026</t>
-  </si>
-  <si>
-    <t>0.6226,0.0031,0.2417,0.0043</t>
-  </si>
-  <si>
-    <t>0.0794,0.0092,0.8841,0.0019</t>
-  </si>
-  <si>
-    <t>0.0000,0.1395,0.0000,0.9985</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9970,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9971,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.8053,0.1865,0.0028,0.0008</t>
-  </si>
-  <si>
-    <t>0.6964,0.2832,0.0099,0.0010</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0005,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9956,0.0013,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9934,0.7604,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9244,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0251,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.0025,0.9940,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9651,0.0025,0.0129,0.0017</t>
-  </si>
-  <si>
-    <t>0.7862,0.0002,0.3013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9441,0.0001,0.0589,0.0002</t>
-  </si>
-  <si>
-    <t>0.0058,0.0000,0.0000,0.9992</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0015,0.9990</t>
-  </si>
-  <si>
-    <t>0.0000,0.9750,0.9853,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0247,0.9579,0.0020,0.0084</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0395,0.9431,0.0039,0.0022</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.7431,0.0002,0.0000,0.5051</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0967,0.9943,0.0008</t>
-  </si>
-  <si>
-    <t>0.9878,0.0001,0.0006,0.0082</t>
-  </si>
-  <si>
-    <t>0.9972,0.0000,0.0002,0.0019</t>
-  </si>
-  <si>
-    <t>0.2702,0.7850,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9966,0.0004,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.1445,0.6067,0.0263,0.0034</t>
-  </si>
-  <si>
-    <t>0.9655,0.0097,0.0050,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0004,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9964,0.0010,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9950,0.0015,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9961,0.0023,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.8164,0.0847,0.0343,0.0032</t>
-  </si>
-  <si>
-    <t>0.2424,0.7566,0.0100,0.0008</t>
-  </si>
-  <si>
-    <t>0.0580,0.0381,0.9475,0.0022</t>
-  </si>
-  <si>
-    <t>0.5854,0.5672,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9874,0.0035,0.0028,0.0019</t>
-  </si>
-  <si>
-    <t>0.9454,0.0384,0.0038,0.0028</t>
-  </si>
-  <si>
-    <t>0.0000,0.0262,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9393,0.0234,0.0143,0.0143</t>
-  </si>
-  <si>
-    <t>0.0009,0.0004,0.9986,0.0005</t>
-  </si>
-  <si>
-    <t>0.0045,0.0249,0.9857,0.0021</t>
-  </si>
-  <si>
-    <t>0.0007,0.0019,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0024,0.0081,0.9932,0.0014</t>
-  </si>
-  <si>
-    <t>0.0091,0.0031,0.9931,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0002,0.9988,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0110,0.0018,0.9790,0.0021</t>
-  </si>
-  <si>
-    <t>0.0230,0.0012,0.9774,0.0008</t>
-  </si>
-  <si>
-    <t>0.0097,0.0042,0.9797,0.0008</t>
-  </si>
-  <si>
-    <t>0.2661,0.0133,0.5734,0.0009</t>
-  </si>
-  <si>
-    <t>0.0023,0.3617,0.9100,0.0007</t>
-  </si>
-  <si>
-    <t>0.0705,0.0025,0.9359,0.0002</t>
-  </si>
-  <si>
-    <t>0.9810,0.0003,0.0084,0.0005</t>
-  </si>
-  <si>
-    <t>0.0238,0.0043,0.9552,0.0036</t>
-  </si>
-  <si>
-    <t>0.0029,0.9925,0.0037,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.9984,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.9939,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.8243,0.2633,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0334,0.9736,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.8832,0.0246,0.0202,0.0007</t>
-  </si>
-  <si>
-    <t>0.9798,0.0004,0.0128,0.0002</t>
-  </si>
-  <si>
-    <t>0.8284,0.0006,0.0045,0.0703</t>
-  </si>
-  <si>
-    <t>0.9414,0.0014,0.0551,0.0001</t>
-  </si>
-  <si>
-    <t>0.2327,0.0002,0.7875,0.0015</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9988,0.0004</t>
-  </si>
-  <si>
-    <t>0.0551,0.0247,0.7824,0.0203</t>
-  </si>
-  <si>
-    <t>0.0022,0.0004,0.9952,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.0011,0.9943,0.0009</t>
-  </si>
-  <si>
-    <t>0.0025,0.2585,0.8830,0.0022</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9937,0.0051,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0022,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9965,0.0033,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9914,0.0098,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0344,0.9957,0.0014</t>
-  </si>
-  <si>
-    <t>0.0017,0.8374,0.8334,0.0003</t>
-  </si>
-  <si>
-    <t>0.9797,0.0002,0.0113,0.0014</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.1278,0.9958,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0006,0.9963,0.0011</t>
-  </si>
-  <si>
-    <t>0.0002,0.0040,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.1216,0.0018,0.8519,0.0074</t>
-  </si>
-  <si>
-    <t>0.9878,0.0005,0.0052,0.0001</t>
-  </si>
-  <si>
-    <t>0.9885,0.0001,0.0103,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9911,0.0107,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9828,0.0152,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9976,0.0024,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9660,0.0461,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0015,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0165,0.9906,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0044,0.2226,0.8054,0.0130</t>
-  </si>
-  <si>
-    <t>0.0169,0.0054,0.9609,0.0018</t>
-  </si>
-  <si>
-    <t>0.0024,0.0003,0.9961,0.0008</t>
-  </si>
-  <si>
-    <t>0.6347,0.0013,0.2076,0.0397</t>
-  </si>
-  <si>
-    <t>0.0293,0.0005,0.9760,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9974,0.0026</t>
-  </si>
-  <si>
-    <t>0.9968,0.0001,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.0042,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0617,0.0002,0.0000,0.9873</t>
-  </si>
-  <si>
-    <t>0.8657,0.0017,0.0003,0.1263</t>
+    <t>0.9720,0.0474,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9882,0.0112,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0026,0.9995,0.0025</t>
+  </si>
+  <si>
+    <t>0.0135,0.1427,0.7740,0.0063</t>
+  </si>
+  <si>
+    <t>0.9598,0.0006,0.0139,0.0061</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0023,0.9990,0.0007</t>
+  </si>
+  <si>
+    <t>0.0014,0.0071,0.9941,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0009,0.9967,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0046,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0761,0.0001,0.9230,0.0027</t>
+  </si>
+  <si>
+    <t>0.9928,0.0004,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.9883,0.0002,0.0065,0.0001</t>
+  </si>
+  <si>
+    <t>0.9956,0.0002,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9783,0.0254,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9890,0.0112,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9947,0.0027,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9961,0.0029,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0021,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0057,0.0196,0.9695,0.0020</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0005</t>
+  </si>
+  <si>
+    <t>0.0047,0.5351,0.4943,0.0233</t>
+  </si>
+  <si>
+    <t>0.0138,0.0021,0.9793,0.0009</t>
+  </si>
+  <si>
+    <t>0.0012,0.0002,0.9980,0.0005</t>
+  </si>
+  <si>
+    <t>0.5533,0.0002,0.1204,0.0584</t>
+  </si>
+  <si>
+    <t>0.0019,0.0007,0.9966,0.0007</t>
+  </si>
+  <si>
+    <t>0.0017,0.0013,0.9905,0.0046</t>
+  </si>
+  <si>
+    <t>0.9690,0.0001,0.0002,0.0471</t>
+  </si>
+  <si>
+    <t>0.0007,0.0043,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.0291,0.0001,0.0001,0.9939</t>
+  </si>
+  <si>
+    <t>0.9961,0.0001,0.0001,0.0017</t>
   </si>
 </sst>
 </file>
@@ -1923,7 +1911,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1937,7 +1925,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1951,7 +1939,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1965,7 +1953,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1979,7 +1967,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1993,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2007,7 +1995,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2021,7 +2009,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2035,7 +2023,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2049,7 +2037,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2063,7 +2051,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2077,7 +2065,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2228,7 +2216,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
         <v>286</v>
@@ -2242,7 +2230,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2326,7 +2314,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2410,7 +2398,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2581,7 +2569,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>285</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2595,7 +2583,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2609,7 +2597,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2623,7 +2611,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2637,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2651,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2665,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2679,7 +2667,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2693,7 +2681,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2707,7 +2695,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2721,7 +2709,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2735,7 +2723,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2749,7 +2737,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2763,7 +2751,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2777,7 +2765,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2791,7 +2779,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2805,7 +2793,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2819,7 +2807,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2833,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2847,7 +2835,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2861,7 +2849,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2875,7 +2863,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2889,7 +2877,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2903,7 +2891,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2917,7 +2905,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2931,7 +2919,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2945,7 +2933,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2959,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2973,7 +2961,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2987,7 +2975,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3001,7 +2989,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3015,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3029,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3043,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3057,7 +3045,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3071,7 +3059,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3085,7 +3073,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3099,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3113,7 +3101,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3127,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3141,7 +3129,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3155,7 +3143,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3169,7 +3157,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3183,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3197,7 +3185,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3211,7 +3199,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3225,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3239,7 +3227,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3253,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3267,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3281,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3295,7 +3283,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3323,7 +3311,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3337,7 +3325,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>271</v>
+        <v>363</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3351,7 +3339,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3365,7 +3353,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3379,7 +3367,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3393,7 +3381,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3407,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>368</v>
+        <v>314</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3421,7 +3409,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3435,7 +3423,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3449,7 +3437,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3463,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3477,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3491,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>285</v>
+        <v>372</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3502,7 +3490,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>373</v>
@@ -3516,7 +3504,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
         <v>374</v>
@@ -3530,7 +3518,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
         <v>375</v>
@@ -3544,7 +3532,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
         <v>376</v>
@@ -3589,7 +3577,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3603,7 +3591,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3617,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3631,7 +3619,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3645,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3656,10 +3644,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3673,7 +3661,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3687,7 +3675,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3701,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3715,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3729,7 +3717,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3743,7 +3731,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3757,7 +3745,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>391</v>
+        <v>358</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3771,7 +3759,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3785,7 +3773,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>393</v>
+        <v>318</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3799,7 +3787,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3813,7 +3801,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3827,7 +3815,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3841,7 +3829,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3855,7 +3843,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3866,10 +3854,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3880,10 +3868,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3897,7 +3885,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3911,7 +3899,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3925,7 +3913,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3939,7 +3927,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3953,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3967,7 +3955,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3981,7 +3969,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3995,7 +3983,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4009,7 +3997,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4023,7 +4011,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4037,7 +4025,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4048,10 +4036,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4065,7 +4053,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4079,7 +4067,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4093,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4107,7 +4095,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4118,10 +4106,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4135,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4149,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4163,7 +4151,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4177,7 +4165,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4191,7 +4179,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4205,7 +4193,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4219,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4233,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4247,7 +4235,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4261,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4275,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4289,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4303,7 +4291,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4317,7 +4305,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4331,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4345,7 +4333,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4359,7 +4347,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4370,10 +4358,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4387,7 +4375,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4401,7 +4389,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4415,7 +4403,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4429,7 +4417,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4443,7 +4431,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4457,7 +4445,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4471,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4485,7 +4473,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4499,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4513,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4527,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4541,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4555,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4569,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4583,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4594,10 +4582,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4608,10 +4596,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4625,7 +4613,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4636,10 +4624,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4653,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4667,7 +4655,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4681,7 +4669,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4695,7 +4683,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4709,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4723,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4737,7 +4725,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4751,7 +4739,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4765,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4776,10 +4764,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4793,7 +4781,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4807,7 +4795,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4821,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4835,7 +4823,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4849,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4863,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4877,7 +4865,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4891,7 +4879,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4905,7 +4893,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4919,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4933,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4947,7 +4935,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4961,7 +4949,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4975,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>391</v>
+        <v>471</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4989,7 +4977,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5000,10 +4988,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5017,7 +5005,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5031,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5045,7 +5033,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5059,7 +5047,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5073,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5087,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5101,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>292</v>
+        <v>480</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5115,7 +5103,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5129,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5143,7 +5131,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5157,7 +5145,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5171,7 +5159,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5185,7 +5173,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5199,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5213,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5227,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5241,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>492</v>
+        <v>401</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5255,7 +5243,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5269,7 +5257,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5283,7 +5271,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>495</v>
+        <v>358</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5297,7 +5285,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5311,7 +5299,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5322,10 +5310,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D245" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5339,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5353,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5367,7 +5355,7 @@
         <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5381,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5395,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5409,7 +5397,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5423,7 +5411,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5437,7 +5425,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5451,7 +5439,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5465,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5479,7 +5467,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
